--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-16.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-16.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261014" sheetId="1" r:id="R8db3c5b0de4f4871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261015" sheetId="1" r:id="Rb51df0122f5e4b6b"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="174">
-  <x:si>
-    <x:t>Daily Holdings (%)  10/14/2026</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
+  <x:si>
+    <x:t>Daily Holdings (%)  10/15/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -52,19 +52,19 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>62,513,858</x:t>
+    <x:t>62,771,618</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$13,834,316,775.40</x:t>
+    <x:t>$13,635,878,578.14</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>20.20%</x:t>
+    <x:t>20.06%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -76,13 +76,13 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>14,937,551</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,423,146,930.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.38%</x:t>
+    <x:t>14,999,141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,333,387,287.25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.32%</x:t>
   </x:si>
   <x:si>
     <x:t>AMD</x:t>
@@ -94,13 +94,13 @@
     <x:t>BBG000BBQCY0</x:t>
   </x:si>
   <x:si>
-    <x:t>6,708,216</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,829,183,857.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.59%</x:t>
+    <x:t>6,735,876</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,787,111,563.48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.57%</x:t>
   </x:si>
   <x:si>
     <x:t>AVGO</x:t>
@@ -112,13 +112,13 @@
     <x:t>BBG00KHY5S69</x:t>
   </x:si>
   <x:si>
-    <x:t>10,906,976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,776,540,440.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.52%</x:t>
+    <x:t>10,952,056</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,771,121,442.48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.55%</x:t>
   </x:si>
   <x:si>
     <x:t>TXN</x:t>
@@ -130,13 +130,13 @@
     <x:t>BBG000BVV7G1</x:t>
   </x:si>
   <x:si>
-    <x:t>11,998,398</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,367,350,398.70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.92%</x:t>
+    <x:t>12,047,988</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,362,834,410.56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.95%</x:t>
   </x:si>
   <x:si>
     <x:t>MU</x:t>
@@ -148,13 +148,67 @@
     <x:t>BBG000C5Z1S3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,401,192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,109,131,642.96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.54%</x:t>
+    <x:t>3,415,212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,180,382,022.88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analog Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BB6G37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,557,256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,052,753,561.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.49%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Asml Holding Nv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000K6MRN4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,826,529</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,027,362,225.76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.45%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRVL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marvell Technology Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG00ZXBJ153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,523,469</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,021,161,661.56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.44%</x:t>
   </x:si>
   <x:si>
     <x:t>KLAC</x:t>
@@ -166,67 +220,13 @@
     <x:t>BBG000BMTFR4</x:t>
   </x:si>
   <x:si>
-    <x:t>17,159,630</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,068,313,440.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.48%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRVL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Marvell Technology Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG00ZXBJ153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,472,049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,059,144,178.72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.47%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Analog Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BB6G37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,526,156</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,037,330,776.92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.44%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASML</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Asml Holding Nv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000K6MRN4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,819,029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,001,397,850.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.38%</x:t>
+    <x:t>17,230,550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,006,041,753.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.42%</x:t>
   </x:si>
   <x:si>
     <x:t>AMAT</x:t>
@@ -238,13 +238,13 @@
     <x:t>BBG000BBPFB9</x:t>
   </x:si>
   <x:si>
-    <x:t>6,694,387</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,989,914,065.81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.37%</x:t>
+    <x:t>6,722,057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,890,551,730.57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.25%</x:t>
   </x:si>
   <x:si>
     <x:t>INTC</x:t>
@@ -256,13 +256,13 @@
     <x:t>BBG000C0G1D1</x:t>
   </x:si>
   <x:si>
-    <x:t>29,543,130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,898,771,915.60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.23%</x:t>
+    <x:t>29,665,230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,829,172,985.10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.16%</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -274,13 +274,31 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>9,937,535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,851,277,542.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.16%</x:t>
+    <x:t>9,978,605</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,768,663,743.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.07%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qualcomm Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000CGC1X8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,960,509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,668,954,805.60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.93%</x:t>
   </x:si>
   <x:si>
     <x:t>SKHY</x:t>
@@ -292,31 +310,13 @@
     <x:t>BBG0238L5JS9</x:t>
   </x:si>
   <x:si>
-    <x:t>17,598,642</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,596,679,627.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.79%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qualcomm Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000CGC1X8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,898,929</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,571,853,123.98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.76%</x:t>
+    <x:t>17,671,202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,581,939,324.22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.80%</x:t>
   </x:si>
   <x:si>
     <x:t>SNPS</x:t>
@@ -328,13 +328,13 @@
     <x:t>BBG000BSFRF3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,013,194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,446,122,196.42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.11%</x:t>
+    <x:t>3,025,644</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,416,334,212.84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.08%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -346,13 +346,31 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,277,355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,409,217,378.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.06%</x:t>
+    <x:t>4,295,035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,393,223,453.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.05%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monolithic Power Systems Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000C30L48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>652,884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$815,582,692.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.20%</x:t>
   </x:si>
   <x:si>
     <x:t>TER</x:t>
@@ -364,31 +382,31 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,308,321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$829,702,900.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.21%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Monolithic Power Systems Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000C30L48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>650,194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$808,262,663.34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.18%</x:t>
+    <x:t>2,317,861</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$795,513,073.81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.17%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NXPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nxp Semiconductors Nv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BND699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,159,723</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$730,180,388.07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.07%</x:t>
   </x:si>
   <x:si>
     <x:t>ALAB</x:t>
@@ -400,31 +418,13 @@
     <x:t>BBG00TDKHW99</x:t>
   </x:si>
   <x:si>
-    <x:t>2,328,582</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$699,226,602.96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.02%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NXPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nxp Semiconductors Nv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BND699</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,146,713</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$694,888,631.79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.01%</x:t>
+    <x:t>2,338,202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$706,090,239.96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.04%</x:t>
   </x:si>
   <x:si>
     <x:t>ARM</x:t>
@@ -436,13 +436,10 @@
     <x:t>BBG01J1GXZF0</x:t>
   </x:si>
   <x:si>
-    <x:t>2,867,033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$682,382,524.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.00%</x:t>
+    <x:t>2,878,883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$704,721,769.57</x:t>
   </x:si>
   <x:si>
     <x:t>STM</x:t>
@@ -454,13 +451,13 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>12,581,108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$590,053,965.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.86%</x:t>
+    <x:t>12,633,108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$588,702,832.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.87%</x:t>
   </x:si>
   <x:si>
     <x:t>MCHP</x:t>
@@ -472,13 +469,13 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,392,665</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$526,727,381.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.77%</x:t>
+    <x:t>7,423,215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$551,247,945.90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.81%</x:t>
   </x:si>
   <x:si>
     <x:t>ON</x:t>
@@ -490,13 +487,13 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,553,658</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$334,056,350.88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.49%</x:t>
+    <x:t>4,572,478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$336,991,628.60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.50%</x:t>
   </x:si>
   <x:si>
     <x:t>-USD CASH-</x:t>
@@ -505,13 +502,13 @@
     <x:t> </x:t>
   </x:si>
   <x:si>
-    <x:t>43,883,894</x:t>
+    <x:t>43,886,374</x:t>
   </x:si>
   <x:si>
     <x:t>Cash Bal</x:t>
   </x:si>
   <x:si>
-    <x:t>$43,883,893.64</x:t>
+    <x:t>$43,886,374.29</x:t>
   </x:si>
   <x:si>
     <x:t>0.06%</x:t>
@@ -523,7 +520,7 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-8,804,655.45</x:t>
+    <x:t>$-9,454,994.81</x:t>
   </x:si>
   <x:si>
     <x:t>-0.01%</x:t>
@@ -1335,7 +1332,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I25" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15" customHeight="1">
@@ -1343,28 +1340,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
+      <x:c r="F26" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
+      <x:c r="H26" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I26" s="1" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="H26" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I26" s="1" t="s">
-        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9" ht="15" customHeight="1">
@@ -1372,28 +1369,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
+      <x:c r="D27" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="E27" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
+      <x:c r="F27" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
+      <x:c r="H27" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I27" s="1" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="H27" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I27" s="1" t="s">
-        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9" ht="15" customHeight="1">
@@ -1401,28 +1398,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
+      <x:c r="D28" s="1" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
+      <x:c r="F28" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
+      <x:c r="H28" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I28" s="1" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="H28" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I28" s="1" t="s">
-        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9" ht="15" customHeight="1">
@@ -1430,28 +1427,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="E29" s="1" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
+      <x:c r="F29" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F29" s="1" t="s">
+      <x:c r="G29" s="1" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G29" s="1" t="s">
+      <x:c r="H29" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I29" s="1" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="H29" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I29" s="1" t="s">
-        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9" ht="15" customHeight="1">
@@ -1462,30 +1459,30 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
+      <x:c r="G30" s="1" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G30" s="1" t="s">
+      <x:c r="H30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I30" s="1" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="H30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I30" s="1" t="s">
-        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9" ht="15" customHeight="1">
       <x:c r="A31" s="2" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
         <x:v>1</x:v>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-16.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-16.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261015" sheetId="1" r:id="Rb51df0122f5e4b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261015" sheetId="1" r:id="R7923a0f0f2b54342"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-16.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-16.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261015" sheetId="1" r:id="R7923a0f0f2b54342"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261015" sheetId="1" r:id="R51a707e48ee647e3"/>
   </x:sheets>
 </x:workbook>
 </file>
